--- a/product_surveys/010_preference_selection_survey--product_surveys.xlsx
+++ b/product_surveys/010_preference_selection_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'ประก'}</t>
+          <t>ประก</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'ประก'}</t>
+          <t>ประก</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'product_a'}</t>
+          <t>product_a</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Product A'}</t>
+          <t>Product A</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'product_b'}</t>
+          <t>product_b</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Product B'}</t>
+          <t>Product B</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'product_c'}</t>
+          <t>product_c</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Product C'}</t>
+          <t>Product C</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'product_a'}</t>
+          <t>product_a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Product A'}</t>
+          <t>Product A</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'product_b'}</t>
+          <t>product_b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Product B'}</t>
+          <t>Product B</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'product_c'}</t>
+          <t>product_c</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Product C'}</t>
+          <t>Product C</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'sms'}</t>
+          <t>sms</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'SMS'}</t>
+          <t>SMS</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'chat'}</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Chat'}</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'10:00_am_-_11:00_am'}</t>
+          <t>10:00_am_-_11:00_am</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': '10:00 AM - 11:00 AM'}</t>
+          <t>10:00 AM - 11:00 AM</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'11:00_am_-_12:00_pm'}</t>
+          <t>11:00_am_-_12:00_pm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': '11:00 AM - 12:00 PM'}</t>
+          <t>11:00 AM - 12:00 PM</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'01:00_pm_-_02:00_pm'}</t>
+          <t>01:00_pm_-_02:00_pm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': '01:00 PM - 02:00 PM'}</t>
+          <t>01:00 PM - 02:00 PM</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'02:00_pm_-_03:00_pm'}</t>
+          <t>02:00_pm_-_03:00_pm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': '02:00 PM - 03:00 PM'}</t>
+          <t>02:00 PM - 03:00 PM</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'03:00_pm_-_04:00_pm'}</t>
+          <t>03:00_pm_-_04:00_pm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': '03:00 PM - 04:00 PM'}</t>
+          <t>03:00 PM - 04:00 PM</t>
         </is>
       </c>
     </row>
